--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget weboldal\dokumentumok\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593EDF5B-4AA2-4D09-A377-16442BFCA784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D76515-7B0D-4D45-8EC6-9022D8CD4128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -46,6 +46,12 @@
   </si>
   <si>
     <t>a global-data.js scriptet csinaltam meg, amibe az alapitvany fontos adatait tarolom (pl nev,adoszam stb). HTML elemkent felhasznalhatoak</t>
+  </si>
+  <si>
+    <t>fájlstruktúra létrehozása, bootstrap importálása, html és css a bootstraphez igazítása</t>
+  </si>
+  <si>
+    <t>navbar és footer elkészítése és globalizálása (egy helyen megírom, minden oldalon betöltöm a nav-footer.js scripttel), template létrehozása</t>
   </si>
 </sst>
 </file>
@@ -99,7 +105,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -377,16 +383,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="126.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="158" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -400,7 +406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46152</v>
       </c>
@@ -414,7 +420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46164</v>
       </c>
@@ -428,7 +434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -440,6 +446,34 @@
       </c>
       <c r="D4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D76515-7B0D-4D45-8EC6-9022D8CD4128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7FD88-71DD-4C53-ABB3-F5D1488585BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>navbar és footer elkészítése és globalizálása (egy helyen megírom, minden oldalon betöltöm a nav-footer.js scripttel), template létrehozása</t>
+  </si>
+  <si>
+    <t>Tovabbi stilus modositasok, impresszum oldal megfelelo adatainak kutatasa, oldalterkep es impresszum oldal elkeszitese, "alapitvany-domain" custom HTML element hozzadasa a global-data.js fajlhoz</t>
   </si>
 </sst>
 </file>
@@ -105,7 +108,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -383,16 +386,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="158" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="181" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -406,7 +409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46152</v>
       </c>
@@ -420,7 +423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46164</v>
       </c>
@@ -434,7 +437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -448,7 +451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46180</v>
       </c>
@@ -462,7 +465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46180</v>
       </c>
@@ -474,6 +477,20 @@
       </c>
       <c r="D6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7FD88-71DD-4C53-ABB3-F5D1488585BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255A2BA3-14D8-45D6-8183-7605010A5262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Tovabbi stilus modositasok, impresszum oldal megfelelo adatainak kutatasa, oldalterkep es impresszum oldal elkeszitese, "alapitvany-domain" custom HTML element hozzadasa a global-data.js fajlhoz</t>
+  </si>
+  <si>
+    <t>Fooldal elkeszitese a megkuldott szoveg alapjan, az elkuldott szovegeket elkezdtem berakni a HTML fajlokba.</t>
   </si>
 </sst>
 </file>
@@ -99,16 +102,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -386,16 +398,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="181" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -409,7 +421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46152</v>
       </c>
@@ -419,11 +431,11 @@
       <c r="C2" s="2">
         <v>0.75694444444444442</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46164</v>
       </c>
@@ -433,11 +445,11 @@
       <c r="C3" s="2">
         <v>0.53125</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -447,11 +459,11 @@
       <c r="C4" s="2">
         <v>0.69444444444444442</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46180</v>
       </c>
@@ -461,11 +473,11 @@
       <c r="C5" s="2">
         <v>0.55555555555555558</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46180</v>
       </c>
@@ -475,11 +487,11 @@
       <c r="C6" s="2">
         <v>0.63541666666666663</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46189</v>
       </c>
@@ -489,11 +501,51 @@
       <c r="C7" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.50347222222222221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D8:D9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255A2BA3-14D8-45D6-8183-7605010A5262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC60632C-DDDF-4867-ABA3-6133763369C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Fooldal elkeszitese a megkuldott szoveg alapjan, az elkuldott szovegeket elkezdtem berakni a HTML fajlokba.</t>
+  </si>
+  <si>
+    <t>tamogatas, rolunk, kuldetesunk, celjaink szovegenek beillesztese, index stilus modositasa, tamogatas css elkeszitese</t>
   </si>
 </sst>
 </file>
@@ -112,10 +115,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -515,7 +518,7 @@
       <c r="C8" s="2">
         <v>0.3611111111111111</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -529,14 +532,20 @@
       <c r="C9" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46191</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>0.50347222222222221</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.53819444444444442</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC60632C-DDDF-4867-ABA3-6133763369C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199A2E9E-B408-46D2-82CD-D5E63DFE85B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>tamogatas, rolunk, kuldetesunk, celjaink szovegenek beillesztese, index stilus modositasa, tamogatas css elkeszitese</t>
+  </si>
+  <si>
+    <t>Kepek leszedese, beillesztése a rolunk oldalra</t>
+  </si>
+  <si>
+    <t>kapcsolat oldal elkészítése</t>
   </si>
 </sst>
 </file>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -549,7 +555,32 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
+      <c r="A11" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199A2E9E-B408-46D2-82CD-D5E63DFE85B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38709F5-D167-4208-A345-C534ACB3950A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>kapcsolat oldal elkészítése</t>
+  </si>
+  <si>
+    <t>Hirek oldal, programunk oldal, stilus elkeszites, kodolas veglegesitese, dokumentalas (nem fejeztem be, tancom van)</t>
+  </si>
+  <si>
+    <t>dokumentacio befejezese (attekintest meg igenyel), 2 todo kiirasa, commit githubra</t>
   </si>
 </sst>
 </file>
@@ -129,7 +135,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -407,16 +413,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="181" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -430,7 +436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46152</v>
       </c>
@@ -444,7 +450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46164</v>
       </c>
@@ -458,7 +464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -472,7 +478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46180</v>
       </c>
@@ -486,7 +492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46180</v>
       </c>
@@ -500,7 +506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46189</v>
       </c>
@@ -514,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46191</v>
       </c>
@@ -528,7 +534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46191</v>
       </c>
@@ -540,7 +546,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46191</v>
       </c>
@@ -554,7 +560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46193</v>
       </c>
@@ -568,7 +574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46218</v>
       </c>
@@ -580,6 +586,34 @@
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.59375</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.78125</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/dokumentumok/munkaido_naplo.xlsx
+++ b/dokumentumok/munkaido_naplo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sedla\Desktop\napfenysziget-alapitvany\dokumentumok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38709F5-D167-4208-A345-C534ACB3950A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC48152D-4012-49E5-AF71-1D4274C30A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>elkezdtem</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>dokumentacio befejezese (attekintest meg igenyel), 2 todo kiirasa, commit githubra</t>
+  </si>
+  <si>
+    <t>PUBLIKALASRA KÉSZ</t>
+  </si>
+  <si>
+    <t>publikálás és az azt követő bugfix-ek</t>
   </si>
 </sst>
 </file>
@@ -135,7 +141,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -413,16 +419,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="181" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -436,7 +442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46152</v>
       </c>
@@ -450,7 +456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46164</v>
       </c>
@@ -464,7 +470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -478,7 +484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46180</v>
       </c>
@@ -492,7 +498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46180</v>
       </c>
@@ -506,7 +512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46189</v>
       </c>
@@ -520,7 +526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46191</v>
       </c>
@@ -534,7 +540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46191</v>
       </c>
@@ -546,7 +552,7 @@
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46191</v>
       </c>
@@ -560,7 +566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46193</v>
       </c>
@@ -574,7 +580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46218</v>
       </c>
@@ -588,7 +594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46265</v>
       </c>
@@ -602,7 +608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46266</v>
       </c>
@@ -614,6 +620,34 @@
       </c>
       <c r="D14" s="4" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
